--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2023.xlsx
@@ -115,12 +115,6 @@
     <t xml:space="preserve">Porvenir</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11402</t>
   </si>
   <si>
@@ -139,12 +133,6 @@
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11102</t>
   </si>
   <si>
@@ -271,6 +259,12 @@
     <t xml:space="preserve">Licantén</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">6308</t>
   </si>
   <si>
@@ -1309,6 +1303,12 @@
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">1402</t>
   </si>
   <si>
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:24</t>
+    <t xml:space="preserve">2026-09-09 20:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2792,7 +2792,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>85.03</v>
+        <v>84.92</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2824,7 +2824,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>84.92</v>
+        <v>84.26</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2856,7 +2856,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>84.26</v>
+        <v>82.79</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2888,7 +2888,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>82.79</v>
+        <v>80.39</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2899,28 +2899,28 @@
         <v>2023</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>81.56</v>
+        <v>96.22</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2931,28 +2931,28 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>80.39</v>
+        <v>93.45</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -2963,28 +2963,28 @@
         <v>2023</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>96.22</v>
+        <v>93.33</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -2995,28 +2995,28 @@
         <v>2023</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>93.45</v>
+        <v>93.21</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>53</v>
@@ -3039,16 +3039,16 @@
         <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>93.33</v>
+        <v>92.8</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3062,7 +3062,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -3071,16 +3071,16 @@
         <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>93.21</v>
+        <v>92.79</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3094,7 +3094,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>57</v>
@@ -3103,16 +3103,16 @@
         <v>58</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>92.8</v>
+        <v>92.58</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3123,28 +3123,28 @@
         <v>2023</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>92.79</v>
+        <v>92.53</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3155,28 +3155,28 @@
         <v>2023</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>92.58</v>
+        <v>92.36</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3187,10 +3187,10 @@
         <v>2023</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>64</v>
@@ -3199,16 +3199,16 @@
         <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>92.53</v>
+        <v>92.28</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3222,7 +3222,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>66</v>
@@ -3231,16 +3231,16 @@
         <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>92.36</v>
+        <v>92.23</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3251,10 +3251,10 @@
         <v>2023</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>68</v>
@@ -3263,16 +3263,16 @@
         <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>92.28</v>
+        <v>91.95</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3283,10 +3283,10 @@
         <v>2023</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3295,16 +3295,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>92.23</v>
+        <v>91.63</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3315,10 +3315,10 @@
         <v>2023</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3327,16 +3327,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>91.95</v>
+        <v>91.57</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3350,7 +3350,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3359,16 +3359,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>91.63</v>
+        <v>91.49</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3379,10 +3379,10 @@
         <v>2023</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3391,16 +3391,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>91.57</v>
+        <v>91.45</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3411,10 +3411,10 @@
         <v>2023</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3423,16 +3423,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>91.49</v>
+        <v>91.32</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3443,10 +3443,10 @@
         <v>2023</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3455,16 +3455,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>91.45</v>
+        <v>91.28</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3475,10 +3475,10 @@
         <v>2023</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3487,16 +3487,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>91.32</v>
+        <v>91.18</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3510,7 +3510,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3519,16 +3519,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>91.18</v>
+        <v>91.17</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3539,28 +3539,28 @@
         <v>2023</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>91.17</v>
+        <v>91.09</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3571,10 +3571,10 @@
         <v>2023</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>89</v>
@@ -3583,16 +3583,16 @@
         <v>90</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>91.09</v>
+        <v>91.02</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3603,10 +3603,10 @@
         <v>2023</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>91</v>
@@ -3615,16 +3615,16 @@
         <v>92</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>91.02</v>
+        <v>90.89</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3635,10 +3635,10 @@
         <v>2023</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>93</v>
@@ -3647,16 +3647,16 @@
         <v>94</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>90.89</v>
+        <v>90.8</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3667,10 +3667,10 @@
         <v>2023</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>95</v>
@@ -3679,16 +3679,16 @@
         <v>96</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>90.8</v>
+        <v>90.78</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3699,10 +3699,10 @@
         <v>2023</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>97</v>
@@ -3711,16 +3711,16 @@
         <v>98</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>90.78</v>
+        <v>90.76</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3731,10 +3731,10 @@
         <v>2023</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>99</v>
@@ -3743,16 +3743,16 @@
         <v>100</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>90.76</v>
+        <v>90.64</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3766,7 +3766,7 @@
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>101</v>
@@ -3775,10 +3775,10 @@
         <v>102</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>103</v>
@@ -3807,16 +3807,16 @@
         <v>104</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>90.64</v>
+        <v>90.51</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3827,10 +3827,10 @@
         <v>2023</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>105</v>
@@ -3839,10 +3839,10 @@
         <v>106</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3859,10 +3859,10 @@
         <v>2023</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>107</v>
@@ -3871,16 +3871,16 @@
         <v>108</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>90.51</v>
+        <v>90.48</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3891,10 +3891,10 @@
         <v>2023</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>109</v>
@@ -3903,16 +3903,16 @@
         <v>110</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>90.48</v>
+        <v>90.47</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3923,10 +3923,10 @@
         <v>2023</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -3935,16 +3935,16 @@
         <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>90.47</v>
+        <v>90.46</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3955,10 +3955,10 @@
         <v>2023</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>113</v>
@@ -3967,16 +3967,16 @@
         <v>114</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>90.46</v>
+        <v>90.43</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -3987,10 +3987,10 @@
         <v>2023</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>115</v>
@@ -3999,16 +3999,16 @@
         <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>90.43</v>
+        <v>90.35</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4019,10 +4019,10 @@
         <v>2023</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>117</v>
@@ -4031,16 +4031,16 @@
         <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>90.35</v>
+        <v>90.21</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4054,7 +4054,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>119</v>
@@ -4063,16 +4063,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>90.21</v>
+        <v>90.15</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4083,10 +4083,10 @@
         <v>2023</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -4095,16 +4095,16 @@
         <v>122</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>90.15</v>
+        <v>90.14</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4118,7 +4118,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>123</v>
@@ -4127,16 +4127,16 @@
         <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>90.14</v>
+        <v>90.08</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4147,10 +4147,10 @@
         <v>2023</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>125</v>
@@ -4159,10 +4159,10 @@
         <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4182,7 +4182,7 @@
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>127</v>
@@ -4191,16 +4191,16 @@
         <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>90.08</v>
+        <v>90.04</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4211,28 +4211,28 @@
         <v>2023</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>129</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>130</v>
+        <v>59</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>90.04</v>
+        <v>90</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4246,19 +4246,19 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4275,10 +4275,10 @@
         <v>2023</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4287,16 +4287,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>90</v>
+        <v>89.96</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4307,10 +4307,10 @@
         <v>2023</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4319,16 +4319,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>89.96</v>
+        <v>89.86</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4339,10 +4339,10 @@
         <v>2023</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4351,16 +4351,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>89.86</v>
+        <v>89.81</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4371,10 +4371,10 @@
         <v>2023</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4383,16 +4383,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>89.81</v>
+        <v>89.76</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4403,10 +4403,10 @@
         <v>2023</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4415,16 +4415,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>89.76</v>
+        <v>89.7</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4435,10 +4435,10 @@
         <v>2023</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4447,16 +4447,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>89.7</v>
+        <v>89.45</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4467,10 +4467,10 @@
         <v>2023</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4479,10 +4479,10 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4499,10 +4499,10 @@
         <v>2023</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4511,16 +4511,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>89.45</v>
+        <v>89.4</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4531,10 +4531,10 @@
         <v>2023</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4543,16 +4543,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>89.4</v>
+        <v>89.38</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4563,10 +4563,10 @@
         <v>2023</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4575,16 +4575,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>89.38</v>
+        <v>89.27</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4607,16 +4607,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>89.27</v>
+        <v>89.24</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4627,10 +4627,10 @@
         <v>2023</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4639,16 +4639,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>89.24</v>
+        <v>89.23</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4659,10 +4659,10 @@
         <v>2023</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4671,10 +4671,10 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4691,10 +4691,10 @@
         <v>2023</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4703,16 +4703,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>89.23</v>
+        <v>89.18</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4723,10 +4723,10 @@
         <v>2023</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4735,10 +4735,10 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4755,10 +4755,10 @@
         <v>2023</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4767,16 +4767,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>89.18</v>
+        <v>89.17</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4787,10 +4787,10 @@
         <v>2023</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4799,16 +4799,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>89.17</v>
+        <v>89.15</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4819,10 +4819,10 @@
         <v>2023</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4831,16 +4831,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>89.15</v>
+        <v>89.11</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4851,10 +4851,10 @@
         <v>2023</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4863,16 +4863,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>89.11</v>
+        <v>89.08</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4886,7 +4886,7 @@
         <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4895,16 +4895,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>89.08</v>
+        <v>89.04</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4915,10 +4915,10 @@
         <v>2023</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4927,16 +4927,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>89.04</v>
+        <v>88.97</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -4947,10 +4947,10 @@
         <v>2023</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4959,16 +4959,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>88.97</v>
+        <v>88.95</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -4979,10 +4979,10 @@
         <v>2023</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -4991,16 +4991,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>88.95</v>
+        <v>88.94</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5011,10 +5011,10 @@
         <v>2023</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5023,16 +5023,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>88.94</v>
+        <v>88.92</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5043,10 +5043,10 @@
         <v>2023</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5055,16 +5055,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>88.92</v>
+        <v>88.91</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5075,10 +5075,10 @@
         <v>2023</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5087,16 +5087,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>88.91</v>
+        <v>88.89</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5107,10 +5107,10 @@
         <v>2023</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5119,16 +5119,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>88.89</v>
+        <v>88.84</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5142,7 +5142,7 @@
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5151,16 +5151,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>88.84</v>
+        <v>88.83</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5171,10 +5171,10 @@
         <v>2023</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5183,16 +5183,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>88.83</v>
+        <v>88.8</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5203,10 +5203,10 @@
         <v>2023</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5215,16 +5215,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>88.8</v>
+        <v>88.77</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5235,10 +5235,10 @@
         <v>2023</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5247,16 +5247,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>88.77</v>
+        <v>88.74</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5267,10 +5267,10 @@
         <v>2023</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5279,16 +5279,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>88.74</v>
+        <v>88.73</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5302,7 +5302,7 @@
         <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5311,16 +5311,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>88.73</v>
+        <v>88.59</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5334,7 +5334,7 @@
         <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5343,16 +5343,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>88.59</v>
+        <v>88.56</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5363,10 +5363,10 @@
         <v>2023</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5375,16 +5375,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>88.56</v>
+        <v>88.55</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5395,10 +5395,10 @@
         <v>2023</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5407,16 +5407,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>88.55</v>
+        <v>88.48</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5430,7 +5430,7 @@
         <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5439,16 +5439,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>88.48</v>
+        <v>88.46</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5459,10 +5459,10 @@
         <v>2023</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5471,16 +5471,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>88.46</v>
+        <v>88.34</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5491,10 +5491,10 @@
         <v>2023</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5503,16 +5503,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>88.34</v>
+        <v>88.31</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5523,10 +5523,10 @@
         <v>2023</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5535,16 +5535,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>88.31</v>
+        <v>88.13</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5555,10 +5555,10 @@
         <v>2023</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5567,16 +5567,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>88.13</v>
+        <v>87.95</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5587,10 +5587,10 @@
         <v>2023</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5599,16 +5599,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>87.95</v>
+        <v>87.92</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5619,10 +5619,10 @@
         <v>2023</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5631,16 +5631,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>87.92</v>
+        <v>87.83</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5651,10 +5651,10 @@
         <v>2023</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5663,16 +5663,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>87.83</v>
+        <v>87.72</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5683,10 +5683,10 @@
         <v>2023</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5695,16 +5695,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>87.72</v>
+        <v>87.69</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5715,10 +5715,10 @@
         <v>2023</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5727,16 +5727,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>87.69</v>
+        <v>87.66</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5747,10 +5747,10 @@
         <v>2023</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5759,16 +5759,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>87.66</v>
+        <v>87.65</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5779,10 +5779,10 @@
         <v>2023</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5791,10 +5791,10 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5811,10 +5811,10 @@
         <v>2023</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5823,16 +5823,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>87.65</v>
+        <v>87.62</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5843,10 +5843,10 @@
         <v>2023</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5855,16 +5855,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>87.62</v>
+        <v>87.57</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5875,10 +5875,10 @@
         <v>2023</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5887,16 +5887,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>87.57</v>
+        <v>87.55</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5907,10 +5907,10 @@
         <v>2023</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5919,16 +5919,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>87.55</v>
+        <v>87.47</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5939,10 +5939,10 @@
         <v>2023</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5951,16 +5951,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>87.47</v>
+        <v>87.46</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -5971,10 +5971,10 @@
         <v>2023</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -5983,16 +5983,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>87.46</v>
+        <v>87.44</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6003,10 +6003,10 @@
         <v>2023</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6015,16 +6015,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>87.44</v>
+        <v>87.43</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6035,10 +6035,10 @@
         <v>2023</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6047,16 +6047,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>87.43</v>
+        <v>87.4</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6067,10 +6067,10 @@
         <v>2023</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6079,16 +6079,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>87.4</v>
+        <v>87.37</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6099,10 +6099,10 @@
         <v>2023</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6111,10 +6111,10 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6131,10 +6131,10 @@
         <v>2023</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6143,16 +6143,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>87.37</v>
+        <v>87.35</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6166,7 +6166,7 @@
         <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6175,16 +6175,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>87.35</v>
+        <v>87.33</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6195,10 +6195,10 @@
         <v>2023</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6207,10 +6207,10 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6227,10 +6227,10 @@
         <v>2023</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6239,16 +6239,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>87.33</v>
+        <v>87.3</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6262,7 +6262,7 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6271,16 +6271,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>87.3</v>
+        <v>87.23</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6291,10 +6291,10 @@
         <v>2023</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6303,16 +6303,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>87.23</v>
+        <v>87.21</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6323,10 +6323,10 @@
         <v>2023</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6335,16 +6335,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>87.21</v>
+        <v>87.19</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6355,10 +6355,10 @@
         <v>2023</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6367,16 +6367,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>87.19</v>
+        <v>87.15</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6387,10 +6387,10 @@
         <v>2023</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6399,16 +6399,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>87.15</v>
+        <v>87.05</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6419,10 +6419,10 @@
         <v>2023</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6431,16 +6431,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>87.05</v>
+        <v>87.02</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6451,10 +6451,10 @@
         <v>2023</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6463,16 +6463,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>87.02</v>
+        <v>87.01</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6483,10 +6483,10 @@
         <v>2023</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6495,16 +6495,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>87.01</v>
+        <v>86.88</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6518,7 +6518,7 @@
         <v>5</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6527,16 +6527,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>86.88</v>
+        <v>86.86</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6547,10 +6547,10 @@
         <v>2023</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6559,10 +6559,10 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6579,10 +6579,10 @@
         <v>2023</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6591,16 +6591,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>86.86</v>
+        <v>86.78</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6611,10 +6611,10 @@
         <v>2023</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6623,16 +6623,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>86.78</v>
+        <v>86.77</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6643,10 +6643,10 @@
         <v>2023</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6655,16 +6655,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>86.77</v>
+        <v>86.68</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6675,10 +6675,10 @@
         <v>2023</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6687,10 +6687,10 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6707,10 +6707,10 @@
         <v>2023</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6719,16 +6719,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>86.68</v>
+        <v>86.66</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6742,7 +6742,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6751,16 +6751,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>86.66</v>
+        <v>86.62</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6774,7 +6774,7 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6783,16 +6783,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>86.62</v>
+        <v>86.5</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6803,10 +6803,10 @@
         <v>2023</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6815,16 +6815,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>86.5</v>
+        <v>86.4</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6835,10 +6835,10 @@
         <v>2023</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6847,16 +6847,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>86.4</v>
+        <v>86.37</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6867,10 +6867,10 @@
         <v>2023</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6879,16 +6879,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>86.37</v>
+        <v>86.34</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6899,10 +6899,10 @@
         <v>2023</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6911,16 +6911,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>86.34</v>
+        <v>86.32</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6934,7 +6934,7 @@
         <v>5</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -6943,16 +6943,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>86.32</v>
+        <v>86.24</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -6963,10 +6963,10 @@
         <v>2023</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -6975,16 +6975,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>86.24</v>
+        <v>86.17</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -6995,10 +6995,10 @@
         <v>2023</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7007,16 +7007,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>86.17</v>
+        <v>86.06</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7027,10 +7027,10 @@
         <v>2023</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7039,16 +7039,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>86.06</v>
+        <v>85.97</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7059,10 +7059,10 @@
         <v>2023</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7071,16 +7071,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>85.97</v>
+        <v>85.87</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7091,10 +7091,10 @@
         <v>2023</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7103,16 +7103,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>85.87</v>
+        <v>85.81</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7123,10 +7123,10 @@
         <v>2023</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7135,16 +7135,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>85.81</v>
+        <v>85.78</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7155,10 +7155,10 @@
         <v>2023</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7167,16 +7167,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>85.78</v>
+        <v>85.74</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7187,10 +7187,10 @@
         <v>2023</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7199,10 +7199,10 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7222,7 +7222,7 @@
         <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7231,16 +7231,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>85.74</v>
+        <v>85.66</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7251,10 +7251,10 @@
         <v>2023</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7263,16 +7263,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>85.66</v>
+        <v>85.64</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7283,10 +7283,10 @@
         <v>2023</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7295,16 +7295,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>85.64</v>
+        <v>85.61</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7318,7 +7318,7 @@
         <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7327,16 +7327,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>85.61</v>
+        <v>85.56</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7350,7 +7350,7 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7359,16 +7359,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>85.56</v>
+        <v>85.4</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7382,7 +7382,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7391,16 +7391,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>85.4</v>
+        <v>85.36</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7411,10 +7411,10 @@
         <v>2023</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7423,16 +7423,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>85.36</v>
+        <v>85.34</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7443,10 +7443,10 @@
         <v>2023</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7455,16 +7455,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>85.34</v>
+        <v>85.2</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7475,10 +7475,10 @@
         <v>2023</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7487,16 +7487,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>85.2</v>
+        <v>85.18</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7510,7 +7510,7 @@
         <v>5</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7519,16 +7519,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>85.18</v>
+        <v>84.98</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7539,10 +7539,10 @@
         <v>2023</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7551,16 +7551,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>84.98</v>
+        <v>84.7</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7574,7 +7574,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7583,16 +7583,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>84.7</v>
+        <v>84.67</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7606,7 +7606,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7615,16 +7615,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>84.67</v>
+        <v>84.65</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7635,10 +7635,10 @@
         <v>2023</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7647,16 +7647,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>84.65</v>
+        <v>84.62</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7667,10 +7667,10 @@
         <v>2023</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7679,16 +7679,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>84.62</v>
+        <v>84.59</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7699,10 +7699,10 @@
         <v>2023</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7711,16 +7711,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>84.59</v>
+        <v>84.54</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7734,7 +7734,7 @@
         <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7743,16 +7743,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>84.54</v>
+        <v>84.52</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7766,7 +7766,7 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7775,16 +7775,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>84.52</v>
+        <v>84.38</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7798,7 +7798,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7807,16 +7807,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>84.38</v>
+        <v>84.3</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7827,10 +7827,10 @@
         <v>2023</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7839,16 +7839,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>84.3</v>
+        <v>84</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7859,10 +7859,10 @@
         <v>2023</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7871,16 +7871,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>84</v>
+        <v>83.82</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7894,7 +7894,7 @@
         <v>5</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7903,16 +7903,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>83.82</v>
+        <v>83.63</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7923,10 +7923,10 @@
         <v>2023</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -7935,16 +7935,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>83.63</v>
+        <v>83.48</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -7958,7 +7958,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -7967,16 +7967,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>83.48</v>
+        <v>83.14</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -7990,7 +7990,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -7999,16 +7999,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>83.14</v>
+        <v>82.68</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8022,7 +8022,7 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8031,16 +8031,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>82.68</v>
+        <v>82.16</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8054,7 +8054,7 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8063,16 +8063,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>82.16</v>
+        <v>81.64</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8083,10 +8083,10 @@
         <v>2023</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8095,16 +8095,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>81.64</v>
+        <v>80.24</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8118,7 +8118,7 @@
         <v>5</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8127,16 +8127,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>80.24</v>
+        <v>79.77</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8147,10 +8147,10 @@
         <v>2023</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8159,16 +8159,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>79.77</v>
+        <v>79.13</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8179,10 +8179,10 @@
         <v>2023</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8191,16 +8191,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>79.13</v>
+        <v>77.94</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8214,7 +8214,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8223,16 +8223,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>77.94</v>
+        <v>76.46</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8243,28 +8243,28 @@
         <v>2023</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>88</v>
+        <v>380</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>47</v>
+        <v>383</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>48</v>
+        <v>384</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>76.46</v>
+        <v>92.93</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8278,25 +8278,25 @@
         <v>4</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D182" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F182" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="E182" s="2" t="s">
+      <c r="G182" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="F182" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>92.93</v>
+        <v>91.61</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8307,28 +8307,28 @@
         <v>2023</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>91.61</v>
+        <v>90.51</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8339,10 +8339,10 @@
         <v>2023</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>390</v>
@@ -8351,16 +8351,16 @@
         <v>391</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>90.51</v>
+        <v>90.29</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8371,10 +8371,10 @@
         <v>2023</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>392</v>
@@ -8383,16 +8383,16 @@
         <v>393</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>90.29</v>
+        <v>90.21</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8403,10 +8403,10 @@
         <v>2023</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>394</v>
@@ -8415,16 +8415,16 @@
         <v>395</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>90.21</v>
+        <v>90.2</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8435,10 +8435,10 @@
         <v>2023</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>396</v>
@@ -8447,16 +8447,16 @@
         <v>397</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>90.2</v>
+        <v>90.15</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8467,10 +8467,10 @@
         <v>2023</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>398</v>
@@ -8479,16 +8479,16 @@
         <v>399</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>90.15</v>
+        <v>90.05</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8502,7 +8502,7 @@
         <v>4</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>400</v>
@@ -8511,16 +8511,16 @@
         <v>401</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>90.05</v>
+        <v>89.91</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8531,28 +8531,28 @@
         <v>2023</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>89.91</v>
+        <v>89.86</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8563,10 +8563,10 @@
         <v>2023</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>405</v>
@@ -8575,16 +8575,16 @@
         <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>89.86</v>
+        <v>89.52</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8595,10 +8595,10 @@
         <v>2023</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>407</v>
@@ -8607,16 +8607,16 @@
         <v>408</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>89.52</v>
+        <v>89.51</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8630,7 +8630,7 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>409</v>
@@ -8639,16 +8639,16 @@
         <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>89.51</v>
+        <v>89.5</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8659,10 +8659,10 @@
         <v>2023</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>411</v>
@@ -8671,16 +8671,16 @@
         <v>412</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>89.5</v>
+        <v>89.1</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8691,10 +8691,10 @@
         <v>2023</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>413</v>
@@ -8703,16 +8703,16 @@
         <v>414</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>89.1</v>
+        <v>89.05</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8723,10 +8723,10 @@
         <v>2023</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>415</v>
@@ -8735,16 +8735,16 @@
         <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>89.05</v>
+        <v>88.78</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8755,28 +8755,28 @@
         <v>2023</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>88.78</v>
+        <v>88.75</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8787,10 +8787,10 @@
         <v>2023</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>419</v>
+        <v>380</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8799,10 +8799,10 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8819,10 +8819,10 @@
         <v>2023</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
@@ -8831,16 +8831,16 @@
         <v>423</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>88.75</v>
+        <v>88.42</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8854,7 +8854,7 @@
         <v>3</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>424</v>
@@ -8863,16 +8863,16 @@
         <v>425</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>88.42</v>
+        <v>87.64</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8886,7 +8886,7 @@
         <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>426</v>
@@ -8895,16 +8895,16 @@
         <v>427</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>87.64</v>
+        <v>87.63</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8915,10 +8915,10 @@
         <v>2023</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>428</v>
@@ -8927,16 +8927,16 @@
         <v>429</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>87.63</v>
+        <v>87.33</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -8950,7 +8950,7 @@
         <v>1</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>430</v>
@@ -8959,10 +8959,10 @@
         <v>431</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -8982,7 +8982,7 @@
         <v>2</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>432</v>
@@ -8991,10 +8991,10 @@
         <v>433</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9014,7 +9014,7 @@
         <v>1</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>434</v>
@@ -9023,10 +9023,10 @@
         <v>435</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9046,7 +9046,7 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>436</v>
@@ -9055,10 +9055,10 @@
         <v>437</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9078,7 +9078,7 @@
         <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>438</v>
@@ -9087,10 +9087,10 @@
         <v>439</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9110,7 +9110,7 @@
         <v>1</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>440</v>
@@ -9119,10 +9119,10 @@
         <v>441</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9142,7 +9142,7 @@
         <v>3</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>442</v>
@@ -9151,10 +9151,10 @@
         <v>443</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9174,19 +9174,19 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>444</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9206,19 +9206,19 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>445</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9238,7 +9238,7 @@
         <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9247,10 +9247,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9270,7 +9270,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9279,10 +9279,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9302,7 +9302,7 @@
         <v>2</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9311,10 +9311,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9334,7 +9334,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9343,10 +9343,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9366,7 +9366,7 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9375,10 +9375,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9398,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9407,10 +9407,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9430,7 +9430,7 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9439,10 +9439,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2023.xlsx
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:14</t>
+    <t xml:space="preserve">2026-09-18 11:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2023.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2023.xlsx
@@ -2056,7 +2056,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:34</t>
+    <t xml:space="preserve">2026-09-24 00:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
